--- a/demand_spreadsheet_model.xlsx
+++ b/demand_spreadsheet_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agaur\YSSP_2023\message_data\message_data\projects\yssp\gaur\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agaur\Passenger_mobility_demand_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5BFE54-57F8-4810-8E23-59197C5CCF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B007CB-8825-49D3-9CEC-CFDF8581E264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="225" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simple_calc" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <author>tc={317F4621-391E-4AA6-9634-81FDCB02EC34}</author>
   </authors>
   <commentList>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{317F4621-391E-4AA6-9634-81FDCB02EC34}">
+    <comment ref="O1" authorId="1" shapeId="0" xr:uid="{317F4621-391E-4AA6-9634-81FDCB02EC34}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="107">
   <si>
     <t>PDT</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>Typical distance_nc</t>
   </si>
 </sst>
 </file>
@@ -896,9 +899,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -936,7 +939,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1042,7 +1045,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1184,7 +1187,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1192,7 +1195,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="N1" dT="2023-11-01T09:53:20.63" personId="{11B3F7A2-9FAD-4562-B5C8-66FFE423C683}" id="{317F4621-391E-4AA6-9634-81FDCB02EC34}">
+  <threadedComment ref="O1" dT="2023-11-01T09:53:20.63" personId="{11B3F7A2-9FAD-4562-B5C8-66FFE423C683}" id="{317F4621-391E-4AA6-9634-81FDCB02EC34}">
     <text xml:space="preserve">Adjusted to reflect commute and distance category
 </text>
   </threadedComment>
@@ -1202,16 +1205,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" customWidth="1"/>
-    <col min="15" max="15" width="23.1796875" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="15" max="15" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1345,7 +1348,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1459,7 +1462,7 @@
         <v>0.65999999999999992</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1513,7 +1516,7 @@
         <v>1.1519999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1548,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1636,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>0.1667952</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>0.18105119999999944</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1802,7 +1805,7 @@
         <v>0.12251250000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
         <v>29</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>0.19815839999999943</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>29</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>0.171072</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>34</v>
       </c>
@@ -1922,7 +1925,7 @@
         <v>0.16822079999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>5</v>
       </c>
@@ -1960,7 +1963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>14</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>1.0078100999999988</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" t="s">
         <v>38</v>
@@ -2029,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>8</v>
       </c>
@@ -2055,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
       <c r="B20" t="s">
         <v>38</v>
@@ -2079,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>39</v>
       </c>
@@ -2105,7 +2108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
       <c r="B22" t="s">
         <v>38</v>
@@ -2129,7 +2132,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H23" t="s">
         <v>40</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
@@ -2172,7 +2175,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2230,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -2253,7 +2256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
         <v>44</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H29" t="s">
         <v>44</v>
       </c>
@@ -2293,7 +2296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H30" t="s">
         <v>44</v>
       </c>
@@ -2313,7 +2316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H31" t="s">
         <v>44</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="H32" t="s">
         <v>44</v>
       </c>
@@ -2353,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
         <v>45</v>
       </c>
@@ -2373,7 +2376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H34" t="s">
         <v>45</v>
       </c>
@@ -2393,7 +2396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H35" t="s">
         <v>45</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H36" t="s">
         <v>45</v>
       </c>
@@ -2433,7 +2436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H37" t="s">
         <v>45</v>
       </c>
@@ -2453,7 +2456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H38" t="s">
         <v>45</v>
       </c>
@@ -2473,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H40" t="s">
         <v>46</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="41" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="8:13" x14ac:dyDescent="0.25">
       <c r="I41" s="7" t="s">
         <v>16</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>1.05833333333333</v>
       </c>
     </row>
-    <row r="42" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="8:13" x14ac:dyDescent="0.25">
       <c r="I42" s="7" t="s">
         <v>19</v>
       </c>
@@ -2527,7 +2530,7 @@
         <v>0.82499999999999996</v>
       </c>
     </row>
-    <row r="43" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="8:13" x14ac:dyDescent="0.25">
       <c r="I43" s="7" t="s">
         <v>22</v>
       </c>
@@ -2544,7 +2547,7 @@
         <v>1.1583333333333301</v>
       </c>
     </row>
-    <row r="44" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="8:13" x14ac:dyDescent="0.25">
       <c r="I44" s="7" t="s">
         <v>25</v>
       </c>
@@ -2561,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="8:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="8:13" x14ac:dyDescent="0.25">
       <c r="I45" s="7" t="s">
         <v>26</v>
       </c>
@@ -2592,31 +2595,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="16.1796875" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" customWidth="1"/>
-    <col min="6" max="6" width="9.54296875" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" customWidth="1"/>
-    <col min="11" max="11" width="10.1796875" customWidth="1"/>
-    <col min="12" max="12" width="23.1796875" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" customWidth="1"/>
-    <col min="14" max="14" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="26.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="23" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="23" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="25" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>47</v>
       </c>
@@ -2633,34 +2638,37 @@
         <v>51</v>
       </c>
       <c r="F1" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="K1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>61</v>
       </c>
@@ -2676,12 +2684,12 @@
       <c r="E2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="14">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
         <v>0.18821664909251201</v>
       </c>
-      <c r="G2" s="14">
-        <v>0</v>
-      </c>
       <c r="H2" s="14">
         <v>0</v>
       </c>
@@ -2698,14 +2706,17 @@
         <v>0</v>
       </c>
       <c r="M2" s="14">
+        <v>0</v>
+      </c>
+      <c r="N2" s="14">
         <v>1.5</v>
       </c>
-      <c r="N2" s="16">
-        <f>(260/365*M2)</f>
+      <c r="O2" s="16">
+        <f>(260/365*N2)</f>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
@@ -2721,36 +2732,39 @@
       <c r="E3" s="14">
         <v>0.5</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="15">
         <v>0.160579817941501</v>
       </c>
-      <c r="G3" s="15">
+      <c r="H3" s="15">
         <v>2.6365740246856801E-2</v>
       </c>
-      <c r="H3" s="15">
+      <c r="I3" s="15">
         <v>4.3023888334934701E-2</v>
       </c>
-      <c r="I3" s="15">
+      <c r="J3" s="15">
         <v>0.79803114155687305</v>
       </c>
-      <c r="J3" s="15">
+      <c r="K3" s="15">
         <v>9.1829962500002305E-2</v>
       </c>
-      <c r="K3" s="15">
+      <c r="L3" s="15">
         <v>1.4818550499814301E-2</v>
       </c>
-      <c r="L3" s="15">
+      <c r="M3" s="15">
         <v>2.0499155348474601E-2</v>
       </c>
-      <c r="M3" s="14">
+      <c r="N3" s="14">
         <v>1.5</v>
       </c>
-      <c r="N3" s="16">
-        <f t="shared" ref="N3:N33" si="0">(260/365*M3)</f>
+      <c r="O3" s="16">
+        <f t="shared" ref="O3:O33" si="0">(260/365*N3)</f>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>61</v>
       </c>
@@ -2766,36 +2780,39 @@
       <c r="E4" s="17">
         <v>3.5</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="G4" s="15">
         <v>0.246012615431391</v>
       </c>
-      <c r="G4" s="15">
+      <c r="H4" s="15">
         <v>6.0754565182454402E-2</v>
       </c>
-      <c r="H4" s="15">
+      <c r="I4" s="15">
         <v>0.18335932947696401</v>
       </c>
-      <c r="I4" s="15">
+      <c r="J4" s="15">
         <v>0.44170968683355999</v>
       </c>
-      <c r="J4" s="15">
+      <c r="K4" s="15">
         <v>0.21809918235390899</v>
       </c>
-      <c r="K4" s="15">
+      <c r="L4" s="15">
         <v>2.8123900052550901E-2</v>
       </c>
-      <c r="L4" s="15">
+      <c r="M4" s="15">
         <v>5.99141683583879E-2</v>
       </c>
-      <c r="M4" s="14">
+      <c r="N4" s="14">
         <v>1.5</v>
       </c>
-      <c r="N4" s="16">
+      <c r="O4" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>61</v>
       </c>
@@ -2811,36 +2828,39 @@
       <c r="E5" s="14">
         <v>8</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="14">
+        <v>8</v>
+      </c>
+      <c r="G5" s="15">
         <v>0.18741879318586499</v>
       </c>
-      <c r="G5" s="15">
+      <c r="H5" s="15">
         <v>8.5327383080475605E-2</v>
       </c>
-      <c r="H5" s="15">
+      <c r="I5" s="15">
         <v>0.27789197204420801</v>
       </c>
-      <c r="I5" s="15">
+      <c r="J5" s="15">
         <v>0.28716273820774701</v>
       </c>
-      <c r="J5" s="15">
+      <c r="K5" s="15">
         <v>0.22764991003763799</v>
       </c>
-      <c r="K5" s="15">
+      <c r="L5" s="15">
         <v>6.79782847909738E-2</v>
       </c>
-      <c r="L5" s="15">
+      <c r="M5" s="15">
         <v>4.6885419238194601E-2</v>
       </c>
-      <c r="M5" s="14">
+      <c r="N5" s="14">
         <v>1.5</v>
       </c>
-      <c r="N5" s="16">
+      <c r="O5" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>61</v>
       </c>
@@ -2856,36 +2876,39 @@
       <c r="E6" s="14">
         <v>15.5</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="G6" s="15">
         <v>0.11683408957076399</v>
       </c>
-      <c r="G6" s="15">
+      <c r="H6" s="15">
         <v>0.15051308714112199</v>
       </c>
-      <c r="H6" s="15">
+      <c r="I6" s="15">
         <v>0.33337442217198698</v>
       </c>
-      <c r="I6" s="15">
+      <c r="J6" s="15">
         <v>5.3198454679054201E-2</v>
       </c>
-      <c r="J6" s="15">
+      <c r="K6" s="15">
         <v>0.24573634096711999</v>
       </c>
-      <c r="K6" s="15">
+      <c r="L6" s="15">
         <v>0.16605167488054101</v>
       </c>
-      <c r="L6" s="15">
+      <c r="M6" s="15">
         <v>4.0633055304625298E-2</v>
       </c>
-      <c r="M6" s="14">
+      <c r="N6" s="14">
         <v>1.5</v>
       </c>
-      <c r="N6" s="16">
+      <c r="O6" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>61</v>
       </c>
@@ -2901,36 +2924,39 @@
       <c r="E7" s="14">
         <v>25.5</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="G7" s="15">
         <v>5.2979087534207103E-2</v>
       </c>
-      <c r="G7" s="15">
+      <c r="H7" s="15">
         <v>0.15709205408832899</v>
       </c>
-      <c r="H7" s="15">
+      <c r="I7" s="15">
         <v>0.257270952131324</v>
       </c>
-      <c r="I7" s="15">
+      <c r="J7" s="15">
         <v>0.126017818840264</v>
       </c>
-      <c r="J7" s="15">
+      <c r="K7" s="15">
         <v>0.15141035296595301</v>
       </c>
-      <c r="K7" s="15">
+      <c r="L7" s="15">
         <v>0.25478835548861001</v>
       </c>
-      <c r="L7" s="15">
+      <c r="M7" s="15">
         <v>4.1221519958062502E-2</v>
       </c>
-      <c r="M7" s="14">
+      <c r="N7" s="14">
         <v>1.5</v>
       </c>
-      <c r="N7" s="16">
+      <c r="O7" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>61</v>
       </c>
@@ -2946,36 +2972,39 @@
       <c r="E8" s="14">
         <v>40.5</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
+        <v>40.5</v>
+      </c>
+      <c r="G8" s="15">
         <v>3.3580289166144597E-2</v>
       </c>
-      <c r="G8" s="15">
+      <c r="H8" s="15">
         <v>0.14759604532526699</v>
       </c>
-      <c r="H8" s="15">
+      <c r="I8" s="15">
         <v>0.22002347523813801</v>
       </c>
-      <c r="I8" s="15">
-        <v>0</v>
-      </c>
       <c r="J8" s="15">
+        <v>0</v>
+      </c>
+      <c r="K8" s="15">
         <v>0.12361338088573801</v>
       </c>
-      <c r="K8" s="15">
+      <c r="L8" s="15">
         <v>0.434092366033136</v>
       </c>
-      <c r="L8" s="15">
+      <c r="M8" s="15">
         <v>6.0037921538530901E-2</v>
       </c>
-      <c r="M8" s="14">
+      <c r="N8" s="14">
         <v>1.5</v>
       </c>
-      <c r="N8" s="16">
+      <c r="O8" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>61</v>
       </c>
@@ -2989,38 +3018,41 @@
         <v>70</v>
       </c>
       <c r="E9" s="14">
+        <v>55</v>
+      </c>
+      <c r="F9" s="14">
         <v>60</v>
       </c>
-      <c r="F9" s="15">
+      <c r="G9" s="15">
         <v>1.4378658077615699E-2</v>
       </c>
-      <c r="G9" s="15">
+      <c r="H9" s="15">
         <v>9.9907430641511905E-2</v>
       </c>
-      <c r="H9" s="15">
+      <c r="I9" s="15">
         <v>0.18700486463576299</v>
       </c>
-      <c r="I9" s="15">
-        <v>0</v>
-      </c>
       <c r="J9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15">
         <v>8.2331904377328693E-2</v>
       </c>
-      <c r="K9" s="15">
+      <c r="L9" s="15">
         <v>0.53343145544756898</v>
       </c>
-      <c r="L9" s="15">
+      <c r="M9" s="15">
         <v>6.8341068532954893E-2</v>
       </c>
-      <c r="M9" s="14">
+      <c r="N9" s="14">
         <v>1.5</v>
       </c>
-      <c r="N9" s="16">
+      <c r="O9" s="16">
         <f t="shared" si="0"/>
         <v>1.0684931506849313</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>61</v>
       </c>
@@ -3037,12 +3069,12 @@
         <f t="shared" ref="E10:E16" si="1">E2</f>
         <v>0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15">
         <v>0.24504891777815199</v>
       </c>
-      <c r="G10" s="15">
-        <v>0</v>
-      </c>
       <c r="H10" s="15">
         <v>0</v>
       </c>
@@ -3058,15 +3090,18 @@
       <c r="L10" s="15">
         <v>0</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="15">
+        <v>0</v>
+      </c>
+      <c r="N10" s="14">
         <v>1.3</v>
       </c>
-      <c r="N10" s="16">
+      <c r="O10" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>61</v>
       </c>
@@ -3083,36 +3118,39 @@
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G11" s="15">
         <v>0.148696165994084</v>
       </c>
-      <c r="G11" s="15">
+      <c r="H11" s="15">
         <v>2.0333765420329698E-2</v>
       </c>
-      <c r="H11" s="15">
+      <c r="I11" s="15">
         <v>2.3655804540991501E-2</v>
       </c>
-      <c r="I11" s="15">
+      <c r="J11" s="15">
         <v>0.78426613119945698</v>
       </c>
-      <c r="J11" s="15">
+      <c r="K11" s="15">
         <v>0.14143918779263001</v>
       </c>
-      <c r="K11" s="15">
+      <c r="L11" s="15">
         <v>5.3248128891353504E-3</v>
       </c>
-      <c r="L11" s="15">
+      <c r="M11" s="15">
         <v>1.9527567069045501E-2</v>
       </c>
-      <c r="M11" s="14">
+      <c r="N11" s="14">
         <v>1.3</v>
       </c>
-      <c r="N11" s="16">
+      <c r="O11" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -3129,36 +3167,39 @@
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="G12" s="15">
         <v>0.28685664566191099</v>
       </c>
-      <c r="G12" s="15">
+      <c r="H12" s="15">
         <v>3.96703669770022E-2</v>
       </c>
-      <c r="H12" s="15">
+      <c r="I12" s="15">
         <v>0.106025174348088</v>
       </c>
-      <c r="I12" s="15">
+      <c r="J12" s="15">
         <v>0.50517989846354605</v>
       </c>
-      <c r="J12" s="15">
+      <c r="K12" s="15">
         <v>0.28837180142015101</v>
       </c>
-      <c r="K12" s="15">
+      <c r="L12" s="15">
         <v>5.0448429480514098E-3</v>
       </c>
-      <c r="L12" s="15">
+      <c r="M12" s="15">
         <v>4.9521740866498097E-2</v>
       </c>
-      <c r="M12" s="14">
+      <c r="N12" s="14">
         <v>1.3</v>
       </c>
-      <c r="N12" s="16">
+      <c r="O12" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -3175,36 +3216,39 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
+        <v>8</v>
+      </c>
+      <c r="G13" s="15">
         <v>0.18072697225569601</v>
       </c>
-      <c r="G13" s="15">
+      <c r="H13" s="15">
         <v>5.0569824263558702E-2</v>
       </c>
-      <c r="H13" s="15">
+      <c r="I13" s="15">
         <v>0.18632765898871201</v>
       </c>
-      <c r="I13" s="15">
+      <c r="J13" s="15">
         <v>0.391250172065705</v>
       </c>
-      <c r="J13" s="15">
+      <c r="K13" s="15">
         <v>0.30094292006974399</v>
       </c>
-      <c r="K13" s="15">
+      <c r="L13" s="15">
         <v>6.7332178581260898E-3</v>
       </c>
-      <c r="L13" s="15">
+      <c r="M13" s="15">
         <v>5.7219877030375302E-2</v>
       </c>
-      <c r="M13" s="14">
+      <c r="N13" s="14">
         <v>1.3</v>
       </c>
-      <c r="N13" s="16">
+      <c r="O13" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
@@ -3221,36 +3265,39 @@
         <f t="shared" si="1"/>
         <v>15.5</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="G14" s="15">
         <v>6.9739598069275502E-2</v>
       </c>
-      <c r="G14" s="15">
+      <c r="H14" s="15">
         <v>8.3280816176077105E-2</v>
       </c>
-      <c r="H14" s="15">
+      <c r="I14" s="15">
         <v>0.314212629088163</v>
       </c>
-      <c r="I14" s="15">
+      <c r="J14" s="15">
         <v>0.14568754867745901</v>
       </c>
-      <c r="J14" s="15">
+      <c r="K14" s="15">
         <v>0.352477571210292</v>
       </c>
-      <c r="K14" s="15">
+      <c r="L14" s="15">
         <v>2.09283348890302E-2</v>
       </c>
-      <c r="L14" s="15">
+      <c r="M14" s="15">
         <v>7.3625586359015199E-2</v>
       </c>
-      <c r="M14" s="14">
+      <c r="N14" s="14">
         <v>1.3</v>
       </c>
-      <c r="N14" s="16">
+      <c r="O14" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>61</v>
       </c>
@@ -3267,36 +3314,39 @@
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="G15" s="15">
         <v>3.48775732631635E-2</v>
       </c>
-      <c r="G15" s="15">
+      <c r="H15" s="15">
         <v>6.7302577026982793E-2</v>
       </c>
-      <c r="H15" s="15">
+      <c r="I15" s="15">
         <v>0.25028456963857398</v>
       </c>
-      <c r="I15" s="15">
+      <c r="J15" s="15">
         <v>0.43292180947654002</v>
       </c>
-      <c r="J15" s="15">
+      <c r="K15" s="15">
         <v>0.15857884585092999</v>
       </c>
-      <c r="K15" s="15">
+      <c r="L15" s="15">
         <v>4.3960436647219797E-2</v>
       </c>
-      <c r="L15" s="15">
+      <c r="M15" s="15">
         <v>3.9122009789789899E-2</v>
       </c>
-      <c r="M15" s="14">
+      <c r="N15" s="14">
         <v>1.3</v>
       </c>
-      <c r="N15" s="16">
+      <c r="O15" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>61</v>
       </c>
@@ -3313,36 +3363,39 @@
         <f t="shared" si="1"/>
         <v>40.5</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="14">
+        <v>40.5</v>
+      </c>
+      <c r="G16" s="18">
         <v>1.7259927547299801E-2</v>
       </c>
-      <c r="G16" s="15">
+      <c r="H16" s="15">
         <v>0.12842094516278199</v>
       </c>
-      <c r="H16" s="15">
+      <c r="I16" s="15">
         <v>0.417603041240518</v>
       </c>
-      <c r="I16" s="15">
-        <v>0</v>
-      </c>
       <c r="J16" s="15">
+        <v>0</v>
+      </c>
+      <c r="K16" s="15">
         <v>0.235491949480815</v>
       </c>
-      <c r="K16" s="15">
+      <c r="L16" s="15">
         <v>0.13164595732414</v>
       </c>
-      <c r="L16" s="15">
+      <c r="M16" s="15">
         <v>6.7824347940976804E-2</v>
       </c>
-      <c r="M16" s="14">
+      <c r="N16" s="14">
         <v>1.3</v>
       </c>
-      <c r="N16" s="16">
+      <c r="O16" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>61</v>
       </c>
@@ -3356,38 +3409,41 @@
         <v>70</v>
       </c>
       <c r="E17" s="14">
+        <v>55</v>
+      </c>
+      <c r="F17" s="14">
         <v>60</v>
       </c>
-      <c r="F17" s="18">
+      <c r="G17" s="18">
         <v>1.6794199430418599E-2</v>
       </c>
-      <c r="G17" s="15">
+      <c r="H17" s="15">
         <v>8.4293103235442896E-2</v>
       </c>
-      <c r="H17" s="15">
+      <c r="I17" s="15">
         <v>0.359447715685911</v>
       </c>
-      <c r="I17" s="15">
-        <v>0</v>
-      </c>
       <c r="J17" s="15">
+        <v>0</v>
+      </c>
+      <c r="K17" s="15">
         <v>0.100050611660432</v>
       </c>
-      <c r="K17" s="15">
+      <c r="L17" s="15">
         <v>0.38351294300633199</v>
       </c>
-      <c r="L17" s="15">
+      <c r="M17" s="15">
         <v>3.8585218926292103E-2</v>
       </c>
-      <c r="M17" s="14">
+      <c r="N17" s="14">
         <v>1.3</v>
       </c>
-      <c r="N17" s="16">
+      <c r="O17" s="16">
         <f t="shared" si="0"/>
         <v>0.92602739726027394</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>61</v>
       </c>
@@ -3404,12 +3460,12 @@
         <f t="shared" ref="E18:E24" si="2">E10</f>
         <v>0</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15">
         <v>0.26606850501711699</v>
       </c>
-      <c r="G18" s="15">
-        <v>0</v>
-      </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
@@ -3425,15 +3481,18 @@
       <c r="L18" s="15">
         <v>0</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="15">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N18" s="16">
+      <c r="O18" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>61</v>
       </c>
@@ -3450,36 +3509,39 @@
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="15">
         <v>0.20118074925951401</v>
       </c>
-      <c r="G19" s="15">
+      <c r="H19" s="15">
         <v>1.42978983785273E-2</v>
       </c>
-      <c r="H19" s="15">
+      <c r="I19" s="15">
         <v>1.60162759590926E-2</v>
       </c>
-      <c r="I19" s="15">
+      <c r="J19" s="15">
         <v>0.80937360145485504</v>
       </c>
-      <c r="J19" s="15">
+      <c r="K19" s="15">
         <v>0.136283799718559</v>
       </c>
-      <c r="K19" s="15">
+      <c r="L19" s="15">
         <v>5.4408844523926502E-3</v>
       </c>
-      <c r="L19" s="15">
+      <c r="M19" s="15">
         <v>1.29968328827312E-2</v>
       </c>
-      <c r="M19" s="14">
+      <c r="N19" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N19" s="16">
+      <c r="O19" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>61</v>
       </c>
@@ -3496,36 +3558,39 @@
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="G20" s="15">
         <v>0.27788246678436701</v>
       </c>
-      <c r="G20" s="15">
+      <c r="H20" s="15">
         <v>3.0543578701592699E-2</v>
       </c>
-      <c r="H20" s="15">
+      <c r="I20" s="15">
         <v>6.5237625979053498E-2</v>
       </c>
-      <c r="I20" s="15">
+      <c r="J20" s="15">
         <v>0.58133350491928604</v>
       </c>
-      <c r="J20" s="15">
+      <c r="K20" s="15">
         <v>0.26128596759078698</v>
       </c>
-      <c r="K20" s="15">
+      <c r="L20" s="15">
         <v>7.3601352390435301E-3</v>
       </c>
-      <c r="L20" s="15">
+      <c r="M20" s="15">
         <v>4.5431166224169102E-2</v>
       </c>
-      <c r="M20" s="14">
+      <c r="N20" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N20" s="16">
+      <c r="O20" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>61</v>
       </c>
@@ -3542,36 +3607,39 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="14">
+        <v>8</v>
+      </c>
+      <c r="G21" s="15">
         <v>0.125240765944791</v>
       </c>
-      <c r="G21" s="15">
+      <c r="H21" s="15">
         <v>4.1972290279187502E-2</v>
       </c>
-      <c r="H21" s="15">
+      <c r="I21" s="15">
         <v>0.16905856365616501</v>
       </c>
-      <c r="I21" s="15">
+      <c r="J21" s="15">
         <v>0.46716728369475402</v>
       </c>
-      <c r="J21" s="15">
+      <c r="K21" s="15">
         <v>0.23484778152316299</v>
       </c>
-      <c r="K21" s="15">
+      <c r="L21" s="15">
         <v>1.8566523013646401E-2</v>
       </c>
-      <c r="L21" s="15">
+      <c r="M21" s="15">
         <v>5.6932014629208501E-2</v>
       </c>
-      <c r="M21" s="14">
+      <c r="N21" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N21" s="16">
+      <c r="O21" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>61</v>
       </c>
@@ -3588,36 +3656,39 @@
         <f t="shared" si="2"/>
         <v>15.5</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="G22" s="15">
         <v>5.1038540575519202E-2</v>
       </c>
-      <c r="G22" s="15">
+      <c r="H22" s="15">
         <v>7.5732006619267295E-2</v>
       </c>
-      <c r="H22" s="15">
+      <c r="I22" s="15">
         <v>0.36643606879656798</v>
       </c>
-      <c r="I22" s="15">
+      <c r="J22" s="15">
         <v>0.11273418537674799</v>
       </c>
-      <c r="J22" s="15">
+      <c r="K22" s="15">
         <v>0.28627427953927098</v>
       </c>
-      <c r="K22" s="15">
+      <c r="L22" s="15">
         <v>8.0641974081875803E-2</v>
       </c>
-      <c r="L22" s="15">
+      <c r="M22" s="15">
         <v>6.2154717187793702E-2</v>
       </c>
-      <c r="M22" s="14">
+      <c r="N22" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N22" s="16">
+      <c r="O22" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>61</v>
       </c>
@@ -3634,36 +3705,39 @@
         <f t="shared" si="2"/>
         <v>25.5</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="G23" s="15">
         <v>3.38169848733322E-2</v>
       </c>
-      <c r="G23" s="15">
+      <c r="H23" s="15">
         <v>5.3649495868314301E-2</v>
       </c>
-      <c r="H23" s="15">
+      <c r="I23" s="15">
         <v>0.29730753417507899</v>
       </c>
-      <c r="I23" s="15">
+      <c r="J23" s="15">
         <v>0.35709054345672597</v>
       </c>
-      <c r="J23" s="15">
+      <c r="K23" s="15">
         <v>0.14221562307608701</v>
       </c>
-      <c r="K23" s="15">
+      <c r="L23" s="15">
         <v>0.106979023094407</v>
       </c>
-      <c r="L23" s="15">
+      <c r="M23" s="15">
         <v>3.1802156273366501E-2</v>
       </c>
-      <c r="M23" s="14">
+      <c r="N23" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N23" s="16">
+      <c r="O23" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>61</v>
       </c>
@@ -3680,36 +3754,39 @@
         <f t="shared" si="2"/>
         <v>40.5</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="14">
+        <v>40.5</v>
+      </c>
+      <c r="G24" s="15">
         <v>2.1238191185474899E-2</v>
       </c>
-      <c r="G24" s="15">
+      <c r="H24" s="15">
         <v>8.3765925403307795E-2</v>
       </c>
-      <c r="H24" s="15">
+      <c r="I24" s="15">
         <v>0.454090064176492</v>
       </c>
-      <c r="I24" s="15">
-        <v>0</v>
-      </c>
       <c r="J24" s="15">
+        <v>0</v>
+      </c>
+      <c r="K24" s="15">
         <v>0.175007801582025</v>
       </c>
-      <c r="K24" s="15">
+      <c r="L24" s="15">
         <v>0.22008059373431199</v>
       </c>
-      <c r="L24" s="15">
+      <c r="M24" s="15">
         <v>4.5735587425206503E-2</v>
       </c>
-      <c r="M24" s="14">
+      <c r="N24" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N24" s="16">
+      <c r="O24" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>61</v>
       </c>
@@ -3723,38 +3800,41 @@
         <v>70</v>
       </c>
       <c r="E25" s="14">
+        <v>55</v>
+      </c>
+      <c r="F25" s="14">
         <v>60</v>
       </c>
-      <c r="F25" s="15">
+      <c r="G25" s="15">
         <v>2.3533796359884701E-2</v>
       </c>
-      <c r="G25" s="15">
+      <c r="H25" s="15">
         <v>6.8333385372376002E-2</v>
       </c>
-      <c r="H25" s="15">
+      <c r="I25" s="15">
         <v>0.43837750835838801</v>
       </c>
-      <c r="I25" s="15">
-        <v>0</v>
-      </c>
       <c r="J25" s="15">
+        <v>0</v>
+      </c>
+      <c r="K25" s="15">
         <v>7.6261074367465403E-2</v>
       </c>
-      <c r="K25" s="15">
+      <c r="L25" s="15">
         <v>0.34827037527496502</v>
       </c>
-      <c r="L25" s="15">
+      <c r="M25" s="15">
         <v>2.99585707997298E-2</v>
       </c>
-      <c r="M25" s="14">
+      <c r="N25" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="N25" s="16">
+      <c r="O25" s="16">
         <f t="shared" si="0"/>
         <v>0.78356164383561644</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>61</v>
       </c>
@@ -3771,12 +3851,12 @@
         <f t="shared" ref="E26:E32" si="3">E18</f>
         <v>0</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15">
         <v>0.38751184134842398</v>
       </c>
-      <c r="G26" s="15">
-        <v>0</v>
-      </c>
       <c r="H26" s="15">
         <v>0</v>
       </c>
@@ -3792,15 +3872,18 @@
       <c r="L26" s="15">
         <v>0</v>
       </c>
-      <c r="M26" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N26" s="16">
+      <c r="M26" s="15">
+        <v>0</v>
+      </c>
+      <c r="N26" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O26" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>61</v>
       </c>
@@ -3817,36 +3900,39 @@
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="15">
         <v>0.142686015388338</v>
       </c>
-      <c r="G27" s="15">
+      <c r="H27" s="15">
         <v>8.0053345109954502E-3</v>
       </c>
-      <c r="H27" s="15">
+      <c r="I27" s="15">
         <v>2.0920585897717701E-2</v>
       </c>
-      <c r="I27" s="15">
+      <c r="J27" s="15">
         <v>0.90072809458036596</v>
       </c>
-      <c r="J27" s="15">
+      <c r="K27" s="15">
         <v>4.7884015418053698E-2</v>
       </c>
-      <c r="K27" s="15">
+      <c r="L27" s="15">
         <v>6.5549352700750201E-3</v>
       </c>
-      <c r="L27" s="15">
+      <c r="M27" s="15">
         <v>9.3722907898837193E-3</v>
       </c>
-      <c r="M27" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N27" s="16">
+      <c r="N27" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O27" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>61</v>
       </c>
@@ -3863,36 +3949,39 @@
         <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="G28" s="15">
         <v>0.179791853763212</v>
       </c>
-      <c r="G28" s="15">
+      <c r="H28" s="15">
         <v>1.8205337195522E-2</v>
       </c>
-      <c r="H28" s="15">
+      <c r="I28" s="15">
         <v>8.1289118094613505E-2</v>
       </c>
-      <c r="I28" s="15">
+      <c r="J28" s="15">
         <v>0.72207796219564202</v>
       </c>
-      <c r="J28" s="15">
+      <c r="K28" s="15">
         <v>0.123784799035439</v>
       </c>
-      <c r="K28" s="15">
+      <c r="L28" s="15">
         <v>7.3067315541823497E-3</v>
       </c>
-      <c r="L28" s="15">
+      <c r="M28" s="15">
         <v>3.57129319501618E-2</v>
       </c>
-      <c r="M28" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N28" s="16">
+      <c r="N28" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O28" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>61</v>
       </c>
@@ -3909,36 +3998,39 @@
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="14">
+        <v>8</v>
+      </c>
+      <c r="G29" s="15">
         <v>0.125667345721832</v>
       </c>
-      <c r="G29" s="15">
+      <c r="H29" s="15">
         <v>2.4788503222838699E-2</v>
       </c>
-      <c r="H29" s="15">
+      <c r="I29" s="15">
         <v>0.18218250715731099</v>
       </c>
-      <c r="I29" s="15">
+      <c r="J29" s="15">
         <v>0.56096940941109696</v>
       </c>
-      <c r="J29" s="15">
+      <c r="K29" s="15">
         <v>0.148707724813786</v>
       </c>
-      <c r="K29" s="15">
+      <c r="L29" s="15">
         <v>1.08391350200286E-2</v>
       </c>
-      <c r="L29" s="15">
+      <c r="M29" s="15">
         <v>5.6497229240758701E-2</v>
       </c>
-      <c r="M29" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N29" s="16">
+      <c r="N29" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O29" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>61</v>
       </c>
@@ -3955,36 +4047,39 @@
         <f t="shared" si="3"/>
         <v>15.5</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="14">
+        <v>15.5</v>
+      </c>
+      <c r="G30" s="15">
         <v>6.6459400258033596E-2</v>
       </c>
-      <c r="G30" s="15">
+      <c r="H30" s="15">
         <v>4.2383306713409098E-2</v>
       </c>
-      <c r="H30" s="15">
+      <c r="I30" s="15">
         <v>0.37442411998430303</v>
       </c>
-      <c r="I30" s="15">
+      <c r="J30" s="15">
         <v>0.22555815661290099</v>
       </c>
-      <c r="J30" s="15">
+      <c r="K30" s="15">
         <v>0.22730908256494201</v>
       </c>
-      <c r="K30" s="15">
+      <c r="L30" s="15">
         <v>2.8747777175390999E-2</v>
       </c>
-      <c r="L30" s="15">
+      <c r="M30" s="15">
         <v>7.90926871290141E-2</v>
       </c>
-      <c r="M30" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N30" s="16">
+      <c r="N30" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O30" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>61</v>
       </c>
@@ -4001,36 +4096,39 @@
         <f t="shared" si="3"/>
         <v>25.5</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="G31" s="15">
         <v>3.8093122659615501E-2</v>
       </c>
-      <c r="G31" s="15">
+      <c r="H31" s="15">
         <v>3.6677211681426097E-2</v>
       </c>
-      <c r="H31" s="15">
+      <c r="I31" s="15">
         <v>0.37693056540617498</v>
       </c>
-      <c r="I31" s="15">
+      <c r="J31" s="15">
         <v>0.31668759976125599</v>
       </c>
-      <c r="J31" s="15">
+      <c r="K31" s="15">
         <v>0.153212938930544</v>
       </c>
-      <c r="K31" s="15">
+      <c r="L31" s="15">
         <v>5.0667100009567902E-2</v>
       </c>
-      <c r="L31" s="15">
+      <c r="M31" s="15">
         <v>4.6219361619082397E-2</v>
       </c>
-      <c r="M31" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N31" s="16">
+      <c r="N31" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O31" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>61</v>
       </c>
@@ -4047,36 +4145,39 @@
         <f t="shared" si="3"/>
         <v>40.5</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="14">
+        <v>40.5</v>
+      </c>
+      <c r="G32" s="15">
         <v>2.5545632303476201E-2</v>
       </c>
-      <c r="G32" s="15">
+      <c r="H32" s="15">
         <v>5.4106656110183497E-2</v>
       </c>
-      <c r="H32" s="15">
+      <c r="I32" s="15">
         <v>0.56704619880551099</v>
       </c>
-      <c r="I32" s="15">
-        <v>0</v>
-      </c>
       <c r="J32" s="15">
+        <v>0</v>
+      </c>
+      <c r="K32" s="15">
         <v>0.15266830509564699</v>
       </c>
-      <c r="K32" s="15">
+      <c r="L32" s="15">
         <v>0.146019170162595</v>
       </c>
-      <c r="L32" s="15">
+      <c r="M32" s="15">
         <v>4.61113884100324E-2</v>
       </c>
-      <c r="M32" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N32" s="16">
+      <c r="N32" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O32" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+        <v>0.54991780821917802</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>61</v>
       </c>
@@ -4090,35 +4191,38 @@
         <v>70</v>
       </c>
       <c r="E33" s="14">
+        <v>55</v>
+      </c>
+      <c r="F33" s="14">
         <v>60</v>
       </c>
-      <c r="F33" s="15">
+      <c r="G33" s="15">
         <v>3.4244788557068903E-2</v>
       </c>
-      <c r="G33" s="15">
+      <c r="H33" s="15">
         <v>3.5745913606355303E-2</v>
       </c>
-      <c r="H33" s="15">
+      <c r="I33" s="15">
         <v>0.50156623831487501</v>
       </c>
-      <c r="I33" s="15">
-        <v>0</v>
-      </c>
       <c r="J33" s="15">
+        <v>0</v>
+      </c>
+      <c r="K33" s="15">
         <v>5.1253210273279899E-2</v>
       </c>
-      <c r="K33" s="15">
+      <c r="L33" s="15">
         <v>0.34187209994191797</v>
       </c>
-      <c r="L33" s="15">
+      <c r="M33" s="15">
         <v>2.2857179541153499E-2</v>
       </c>
-      <c r="M33" s="14">
-        <v>0.8</v>
-      </c>
-      <c r="N33" s="16">
+      <c r="N33" s="20">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="O33" s="16">
         <f t="shared" si="0"/>
-        <v>0.56986301369863013</v>
+        <v>0.54991780821917802</v>
       </c>
     </row>
   </sheetData>
@@ -4131,24 +4235,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S25"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="2" max="2" width="9.90625" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="8.453125" customWidth="1"/>
-    <col min="12" max="12" width="9.81640625" customWidth="1"/>
-    <col min="14" max="14" width="11.81640625" customWidth="1"/>
-    <col min="15" max="15" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" customWidth="1"/>
-    <col min="17" max="17" width="11.54296875" customWidth="1"/>
-    <col min="18" max="18" width="14.90625" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>47</v>
       </c>
@@ -4188,7 +4292,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -4228,7 +4332,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -4280,7 +4384,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -4332,7 +4436,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -4378,7 +4482,7 @@
         <v>4110540076.778142</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -4424,7 +4528,7 @@
         <v>257416265.38227236</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -4470,7 +4574,7 @@
         <v>1340176274.8581724</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>87</v>
       </c>
@@ -4485,7 +4589,7 @@
         <v>20388296.905200001</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -4500,7 +4604,7 @@
         <v>20388296.905200001</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -4515,7 +4619,7 @@
         <v>20388296.905200001</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -4530,7 +4634,7 @@
         <v>20388296.905200001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -4545,7 +4649,7 @@
         <v>20388296.905200001</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -4560,7 +4664,7 @@
         <v>24465956.28624</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -4575,7 +4679,7 @@
         <v>24465956.28624</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -4590,7 +4694,7 @@
         <v>24465956.28624</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -4605,7 +4709,7 @@
         <v>24465956.28624</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -4620,7 +4724,7 @@
         <v>24465956.28624</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -4636,7 +4740,7 @@
       </c>
       <c r="P18" s="23"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -4653,7 +4757,7 @@
       <c r="O19" s="22"/>
       <c r="P19" s="23"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -4670,7 +4774,7 @@
       <c r="O20" s="22"/>
       <c r="P20" s="23"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -4687,7 +4791,7 @@
       <c r="O21" s="22"/>
       <c r="P21" s="23"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -4704,14 +4808,14 @@
       <c r="O22" s="22"/>
       <c r="P22" s="23"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C23" s="14"/>
       <c r="P23" s="23"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="P24" s="23"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>87</v>
       </c>
@@ -4742,14 +4846,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD366040-A366-4612-8000-D8C58CA34DFB}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>97</v>
       </c>
@@ -4760,7 +4864,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -4771,7 +4875,7 @@
         <v>978.50800000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -4783,7 +4887,7 @@
         <v>4657.6980800000001</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -4794,7 +4898,7 @@
         <v>887.1805866666673</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -4805,7 +4909,7 @@
         <v>8.0522740000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -4816,7 +4920,7 @@
         <v>49.602007840000013</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -4827,7 +4931,7 @@
         <v>9.4480014933333365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -4838,7 +4942,7 @@
         <v>16.093</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
@@ -4849,7 +4953,7 @@
         <v>121.66307999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -4860,7 +4964,7 @@
         <v>23.17392000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>100</v>
       </c>
@@ -4871,7 +4975,7 @@
         <v>4.5739999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>100</v>
       </c>
@@ -4882,7 +4986,7 @@
         <v>28.175840000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>100</v>
       </c>
@@ -4893,7 +4997,7 @@
         <v>5.3668266666666682</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>101</v>
       </c>
@@ -4904,7 +5008,7 @@
         <v>14.397443772284356</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>101</v>
       </c>
@@ -4915,7 +5019,7 @@
         <v>2.742370242339879</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>102</v>
       </c>
@@ -4926,7 +5030,7 @@
         <v>0.37485093796559932</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -4937,7 +5041,7 @@
         <v>7.1400178660114166E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -4948,7 +5052,7 @@
         <v>14.6706625897452</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -4959,7 +5063,7 @@
         <v>2.7944119218562289</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -4970,7 +5074,7 @@
         <v>0.91921444797902263</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -4981,7 +5085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>104</v>
       </c>
@@ -4992,7 +5096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -5003,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -5014,7 +5118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>104</v>
       </c>
@@ -5025,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -5036,7 +5140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -5047,7 +5151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -5058,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -5069,7 +5173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -5080,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>87</v>
       </c>
@@ -5091,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -5102,7 +5206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -5113,7 +5217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -5124,7 +5228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -5135,7 +5239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -5146,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -5157,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>100</v>
       </c>
@@ -5168,7 +5272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>101</v>
       </c>
@@ -5179,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>101</v>
       </c>
@@ -5190,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>101</v>
       </c>
@@ -5201,7 +5305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>101</v>
       </c>
@@ -5212,7 +5316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>102</v>
       </c>
@@ -5223,7 +5327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>102</v>
       </c>
@@ -5234,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>102</v>
       </c>
@@ -5245,7 +5349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -5256,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -5267,7 +5371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>103</v>
       </c>
@@ -5278,7 +5382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>103</v>
       </c>
